--- a/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE7233F-2B9E-45A4-BD4C-E12B882485FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2101755-FA8C-4B4D-823B-D5A00EBEB4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3516" yWindow="3516" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -137,14 +137,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"IntentId":1,"Value":9}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"IntentId":1,"Value":12}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"IntentId":1,"Value":26},{"IntentId":2,"Value":4}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -154,6 +146,14 @@
   </si>
   <si>
     <t>[{"IntentId":0,"Value":4}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":5,"Value":3}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":4,"Value":6}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -694,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -743,7 +743,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -820,7 +820,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -842,7 +842,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -853,7 +853,7 @@
         <v>21</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -864,23 +864,8 @@
         <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2101755-FA8C-4B4D-823B-D5A00EBEB4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAC2EEF-07CC-46F4-AE23-1CBC7EDD8716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,10 +125,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"IntentId":2,"Value":4}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"IntentId":1,"Value":11}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -154,6 +150,10 @@
   </si>
   <si>
     <t>[{"IntentId":4,"Value":6}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":2,"Value":15}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -743,7 +743,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -787,7 +787,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -798,7 +798,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -809,7 +809,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -820,7 +820,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -842,7 +842,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -853,7 +853,7 @@
         <v>21</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -864,7 +864,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAC2EEF-07CC-46F4-AE23-1CBC7EDD8716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3723F670-DD04-445A-BFEF-63E4EEE8DBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -154,6 +154,22 @@
   </si>
   <si>
     <t>[{"IntentId":2,"Value":15}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉睡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>唤醒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":6,"Value":0}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -694,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -867,6 +883,44 @@
         <v>26</v>
       </c>
     </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3723F670-DD04-445A-BFEF-63E4EEE8DBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB22B805-C9C7-4E10-9B73-01965A706F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -170,6 +170,10 @@
   </si>
   <si>
     <t>[{"IntentId":6,"Value":0}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":5,"Value":13}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -902,7 +906,7 @@
         <v>32</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -913,7 +917,7 @@
         <v>33</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
